--- a/notes/Lighting_PowerProfile_Calibration.xlsx
+++ b/notes/Lighting_PowerProfile_Calibration.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\GitHub\PulSar\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9848D8E-263C-4EC5-8A99-5F4E773002CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C23CBD-2C87-42BF-9D1B-5A6C12EA48CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5542" yWindow="14325" windowWidth="8858" windowHeight="1155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Measured Stock" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Description</t>
   </si>
@@ -93,6 +94,9 @@
   </si>
   <si>
     <t>Black 12v, build a light show</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws2815 rgb 5m strip, 3.1A </t>
   </si>
 </sst>
 </file>
@@ -812,7 +816,7 @@
         <v>0.51300000000000001</v>
       </c>
       <c r="K18">
-        <f t="shared" ref="K18:K21" si="2">$J$3*D18</f>
+        <f t="shared" ref="K18" si="2">$J$3*D18</f>
         <v>0.57000000000000006</v>
       </c>
     </row>
@@ -838,7 +842,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <f t="shared" ref="K20:K22" si="3">$J$3*D20</f>
+        <f t="shared" ref="K20:K21" si="3">$J$3*D20</f>
         <v>5.7</v>
       </c>
     </row>
@@ -876,4 +880,22 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7962EAB6-F4C8-4F88-97E0-274EFD73F062}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>